--- a/data/trans_dic/ProblemasDormirP33b-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,64; 28,72</t>
+          <t>21,83; 29,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,0; 39,39</t>
+          <t>33,69; 39,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,66; 34,24</t>
+          <t>29,6; 33,94</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,87</t>
+          <t>6,42; 11,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 16,53</t>
+          <t>10,9; 16,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,34</t>
+          <t>9,64; 13,42</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 14,91</t>
+          <t>9,21; 14,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,88; 17,54</t>
+          <t>12,86; 17,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,55; 15,48</t>
+          <t>11,46; 15,24</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 13,49</t>
+          <t>9,49; 13,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,12; 20,84</t>
+          <t>15,42; 20,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 16,94</t>
+          <t>13,52; 16,94</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>111455; 147905</t>
+          <t>112415; 149552</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>256876; 297566</t>
+          <t>254545; 296515</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>376816; 435007</t>
+          <t>376094; 431184</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>150943; 248880</t>
+          <t>147067; 252693</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>235713; 369981</t>
+          <t>243834; 368334</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>414760; 604264</t>
+          <t>436494; 607526</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59035; 96405</t>
+          <t>59563; 95976</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85088; 115827</t>
+          <t>84933; 117801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>150958; 202362</t>
+          <t>149770; 199236</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>325997; 465529</t>
+          <t>327611; 468230</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>552520; 761376</t>
+          <t>563469; 756062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>971342; 1203844</t>
+          <t>960797; 1203699</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProblemasDormirP33b-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,83; 29,04</t>
+          <t>20,65; 27,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,69; 39,25</t>
+          <t>34,13; 39,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,6; 33,94</t>
+          <t>29,22; 33,69</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 11,03</t>
+          <t>9,27; 11,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 16,46</t>
+          <t>15,3; 18,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 13,42</t>
+          <t>12,59; 14,58</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,21; 14,84</t>
+          <t>9,13; 14,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 17,84</t>
+          <t>12,96; 17,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,46; 15,24</t>
+          <t>11,96; 15,44</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,56</t>
+          <t>11,83; 14,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,42; 20,69</t>
+          <t>19,53; 21,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,52; 16,94</t>
+          <t>16,23; 17,89</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>128248</t>
+          <t>138058</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>275570</t>
+          <t>301294</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403818</t>
+          <t>439352</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>112415; 149552</t>
+          <t>119461; 157628</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>254545; 296515</t>
+          <t>280549; 322449</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>376094; 431184</t>
+          <t>409285; 471806</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>212174</t>
+          <t>234656</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>319978</t>
+          <t>361716</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>532152</t>
+          <t>596373</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>147067; 252693</t>
+          <t>206828; 266289</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>243834; 368334</t>
+          <t>332177; 394831</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>436494; 607526</t>
+          <t>554051; 641593</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75132</t>
+          <t>84295</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>99804</t>
+          <t>112670</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174936</t>
+          <t>196965</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59563; 95976</t>
+          <t>64940; 104890</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84933; 117801</t>
+          <t>95254; 129746</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149770; 199236</t>
+          <t>173043; 223293</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>415554</t>
+          <t>457009</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>695352</t>
+          <t>775680</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1110906</t>
+          <t>1232689</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>327611; 468230</t>
+          <t>416449; 501093</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>563469; 756062</t>
+          <t>728042; 814736</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>960797; 1203699</t>
+          <t>1176169; 1296996</t>
         </is>
       </c>
     </row>
